--- a/Design and Operations/Building the hardware/HIW3_Hardware_Assembly_Parts_2025.xlsx
+++ b/Design and Operations/Building the hardware/HIW3_Hardware_Assembly_Parts_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashleyhsieh/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5380FE8-4430-CB44-B058-CE58B5F86CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7023C94-48F7-1D42-BDBD-F1BF203140A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1700" yWindow="760" windowWidth="29280" windowHeight="18880" xr2:uid="{A087A4C0-4E06-0E4E-9B7C-0A1BE8616E01}"/>
+    <workbookView xWindow="40" yWindow="760" windowWidth="29280" windowHeight="18880" xr2:uid="{A087A4C0-4E06-0E4E-9B7C-0A1BE8616E01}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="234">
   <si>
     <t>Category/Name</t>
   </si>
@@ -717,6 +717,27 @@
   </si>
   <si>
     <t>147.9 (case of 10)</t>
+  </si>
+  <si>
+    <t>HARFINGTON 12pcs 16Gauge Stainless Steel Dispensing Needles, 1 1/2”</t>
+  </si>
+  <si>
+    <t>HARFINGTON 12pcs 16Gauge Stainless Steel Dispensing Needles, 1”</t>
+  </si>
+  <si>
+    <t>B0CR1V3JDV</t>
+  </si>
+  <si>
+    <t>B0CR1RB6Z7</t>
+  </si>
+  <si>
+    <t>7.29 (pack of 10)</t>
+  </si>
+  <si>
+    <t>8.59 ( pack of 10)</t>
+  </si>
+  <si>
+    <t>Same thing, choose the proper length for your setups.</t>
   </si>
 </sst>
 </file>
@@ -791,7 +812,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -816,6 +837,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1150,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51783EC7-9479-8048-9347-E5CE345B4998}">
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
@@ -2755,13 +2777,49 @@
         <v>180</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A74" s="6"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A75" s="6"/>
+    <row r="74" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A74" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B74" s="5">
+        <v>4</v>
+      </c>
+      <c r="C74" t="s">
+        <v>110</v>
+      </c>
+      <c r="D74" t="s">
+        <v>229</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F74" s="5">
+        <v>8.59</v>
+      </c>
+      <c r="G74" s="12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A75" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B75" s="5">
+        <v>4</v>
+      </c>
+      <c r="C75" t="s">
+        <v>110</v>
+      </c>
+      <c r="D75" t="s">
+        <v>230</v>
+      </c>
+      <c r="E75" t="s">
+        <v>231</v>
+      </c>
+      <c r="F75" s="5">
+        <v>7.29</v>
+      </c>
+      <c r="G75" s="12"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="6"/>
@@ -2847,14 +2905,12 @@
     <row r="103" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A103" s="6"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A104" s="6"/>
-    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="C39:D39"/>
+    <mergeCell ref="G74:G75"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
